--- a/excel/cifar10_resnet44_retrained.xlsx
+++ b/excel/cifar10_resnet44_retrained.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.314448315626497</v>
+        <v>2.315808110935673</v>
       </c>
     </row>
   </sheetData>
